--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="69">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -73,6 +76,24 @@
     <t>2026-05-15</t>
   </si>
   <si>
+    <t>2026-05-19</t>
+  </si>
+  <si>
+    <t>2026-05-24</t>
+  </si>
+  <si>
+    <t>2026-05-31</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1167 В. Търново вход</t>
+  </si>
+  <si>
     <t>В6202ВС</t>
   </si>
   <si>
@@ -103,25 +124,85 @@
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>07:27</t>
-  </si>
-  <si>
-    <t>16:25</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>10:22</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>01:57</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>18:25:00</t>
+  </si>
+  <si>
+    <t>07:27:00</t>
+  </si>
+  <si>
+    <t>16:24:00</t>
+  </si>
+  <si>
+    <t>13:38:00</t>
+  </si>
+  <si>
+    <t>10:22:00</t>
+  </si>
+  <si>
+    <t>14:31:00</t>
+  </si>
+  <si>
+    <t>01:58:00</t>
+  </si>
+  <si>
+    <t>20:37:00</t>
+  </si>
+  <si>
+    <t>04:41:00</t>
+  </si>
+  <si>
+    <t>19:29:00</t>
+  </si>
+  <si>
+    <t>08:00:00</t>
+  </si>
+  <si>
+    <t>18:48:00</t>
+  </si>
+  <si>
+    <t>16:48:00</t>
+  </si>
+  <si>
+    <t>3231460809 3231460809</t>
+  </si>
+  <si>
+    <t>3231589418 3231589418</t>
+  </si>
+  <si>
+    <t>3231789999 3231789999</t>
+  </si>
+  <si>
+    <t>3231831135 3231831135</t>
+  </si>
+  <si>
+    <t>3231829050 3231829050</t>
+  </si>
+  <si>
+    <t>3231878739 3231878739</t>
+  </si>
+  <si>
+    <t>3231914403 3231914403</t>
+  </si>
+  <si>
+    <t>3232110352 3232110352</t>
+  </si>
+  <si>
+    <t>3232313386 3232313386</t>
+  </si>
+  <si>
+    <t>3232345673 3232345673</t>
+  </si>
+  <si>
+    <t>3232647357 3232647357</t>
+  </si>
+  <si>
+    <t>3232675876 3232675876</t>
+  </si>
+  <si>
+    <t>3232677533 3232677533</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОК ТРАНС ЕООД</t>
@@ -545,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -554,16 +635,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -603,385 +685,673 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2">
-        <v>1147</v>
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>150.02</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2">
         <v>1.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>249.03</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.8</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>270.04</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="M2">
-        <v>176858</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3">
-        <v>1199</v>
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F3">
         <v>65</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3">
         <v>1.65</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>107.25</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.79</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>116.35</v>
       </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>38</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="M3">
-        <v>265066</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4">
-        <v>1199</v>
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F4">
         <v>162</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4">
         <v>1.65</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>267.3</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.79</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>289.98</v>
       </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="M4">
-        <v>266251</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5">
-        <v>1199</v>
+        <v>17</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F5">
         <v>162.73</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5">
         <v>1.65</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>268.5</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.78</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>289.66</v>
       </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="M5">
-        <v>266463</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6">
-        <v>1147</v>
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F6">
         <v>44.33</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6">
         <v>1.47</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>65.17</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.54</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>68.27</v>
       </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="M6">
-        <v>181034</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7">
-        <v>1167</v>
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F7">
         <v>147</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7">
         <v>1.65</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>242.55</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.77</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>260.19</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>42</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
         <v>34</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>138139</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8">
-        <v>1147</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
       </c>
       <c r="F8">
         <v>71.3</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8">
         <v>1.64</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>116.93</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.76</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>125.49</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9">
+        <v>58.79</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9">
+        <v>1.63</v>
+      </c>
+      <c r="I9" s="1">
+        <v>95.83</v>
+      </c>
+      <c r="J9">
+        <v>1.75</v>
+      </c>
+      <c r="K9" s="1">
+        <v>102.88</v>
+      </c>
+      <c r="L9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10">
+        <v>163</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10">
+        <v>1.63</v>
+      </c>
+      <c r="I10" s="1">
+        <v>265.69</v>
+      </c>
+      <c r="J10">
+        <v>1.72</v>
+      </c>
+      <c r="K10" s="1">
+        <v>280.36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11">
+        <v>1.63</v>
+      </c>
+      <c r="I11" s="1">
+        <v>105.95</v>
+      </c>
+      <c r="J11">
+        <v>1.72</v>
+      </c>
+      <c r="K11" s="1">
+        <v>111.8</v>
+      </c>
+      <c r="L11" t="s">
+        <v>46</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12">
+        <v>131.01</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H12">
+        <v>1.61</v>
+      </c>
+      <c r="I12" s="1">
+        <v>210.93</v>
+      </c>
+      <c r="J12">
+        <v>1.69</v>
+      </c>
+      <c r="K12" s="1">
+        <v>221.41</v>
+      </c>
+      <c r="L12" t="s">
+        <v>47</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
         <v>35</v>
       </c>
-      <c r="L8">
+      <c r="F13">
+        <v>46</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13">
+        <v>1.52</v>
+      </c>
+      <c r="I13" s="1">
+        <v>69.92</v>
+      </c>
+      <c r="J13">
+        <v>1.57</v>
+      </c>
+      <c r="K13" s="1">
+        <v>72.22</v>
+      </c>
+      <c r="L13" t="s">
+        <v>48</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="M8">
-        <v>181443</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="3" t="s">
+      <c r="N13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14">
+        <v>48</v>
+      </c>
+      <c r="G14" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="6">
-        <v>758.05</v>
-      </c>
-      <c r="C13" s="6">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.651</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1251.56</v>
-      </c>
-      <c r="F13" s="6">
-        <v>1351.71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="6">
-        <v>44.33</v>
-      </c>
-      <c r="C14" s="6">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1.4701</v>
-      </c>
-      <c r="E14" s="6">
-        <v>65.17</v>
-      </c>
-      <c r="F14" s="6">
-        <v>68.27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="9">
-        <v>802.38</v>
-      </c>
-      <c r="C15" s="9">
-        <v>7</v>
-      </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="9">
-        <v>1316.73</v>
-      </c>
-      <c r="F15" s="9">
-        <v>1419.98</v>
+      <c r="H14">
+        <v>1.61</v>
+      </c>
+      <c r="I14" s="1">
+        <v>77.28</v>
+      </c>
+      <c r="J14">
+        <v>1.69</v>
+      </c>
+      <c r="K14" s="1">
+        <v>81.12</v>
+      </c>
+      <c r="L14" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1223.85</v>
+      </c>
+      <c r="C19" s="6">
+        <v>11</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.6401</v>
+      </c>
+      <c r="E19" s="6">
+        <v>2007.24</v>
+      </c>
+      <c r="F19" s="6">
+        <v>2149.28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B20" s="6">
+        <v>90.33</v>
+      </c>
+      <c r="C20" s="6">
+        <v>2</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1.4955</v>
+      </c>
+      <c r="E20" s="6">
+        <v>135.09</v>
+      </c>
+      <c r="F20" s="6">
+        <v>140.49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B21" s="9">
+        <v>1314.18</v>
+      </c>
+      <c r="C21" s="9">
+        <v>13</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="9">
+        <v>2142.33</v>
+      </c>
+      <c r="F21" s="9">
+        <v>2289.77</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -256,7 +256,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -266,12 +266,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -321,17 +315,17 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="54">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,6 +52,12 @@
     <t>Час</t>
   </si>
   <si>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-06-02</t>
   </si>
   <si>
@@ -64,10 +73,13 @@
     <t>2026-06-24</t>
   </si>
   <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>2026-06-26</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В6282ТT</t>
@@ -97,25 +109,55 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-06-02 19:45:54</t>
-  </si>
-  <si>
-    <t>2026-06-08 20:12:24</t>
-  </si>
-  <si>
-    <t>2026-06-11 20:08:16</t>
-  </si>
-  <si>
-    <t>2026-06-11 21:27:36</t>
-  </si>
-  <si>
-    <t>2026-06-15 11:03:36</t>
-  </si>
-  <si>
-    <t>2026-06-24 11:23:42</t>
-  </si>
-  <si>
-    <t>2026-06-24 15:52:56</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>19:45:00</t>
+  </si>
+  <si>
+    <t>20:13:00</t>
+  </si>
+  <si>
+    <t>20:08:00</t>
+  </si>
+  <si>
+    <t>21:28:00</t>
+  </si>
+  <si>
+    <t>11:03:00</t>
+  </si>
+  <si>
+    <t>11:24:00</t>
+  </si>
+  <si>
+    <t>15:53:00</t>
+  </si>
+  <si>
+    <t>15:51:00</t>
+  </si>
+  <si>
+    <t>3232768773 3232768773</t>
+  </si>
+  <si>
+    <t>3233064469 3233064469</t>
+  </si>
+  <si>
+    <t>3233201867 3233201867</t>
+  </si>
+  <si>
+    <t>3233210758 3233210758</t>
+  </si>
+  <si>
+    <t>3233385107 3233385107</t>
+  </si>
+  <si>
+    <t>3233806319 3233806319</t>
+  </si>
+  <si>
+    <t>3233823367 3233823367</t>
+  </si>
+  <si>
+    <t>3233956812 3233956812</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОК ТРАНС ЕООД</t>
@@ -533,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -542,14 +584,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -583,323 +628,439 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F2">
         <v>62</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2">
         <v>1.6</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>99.2</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.69</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>104.78</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F3">
         <v>53.83</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3">
         <v>1.57</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>84.51000000000001</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.64</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>88.28</v>
       </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F4">
         <v>71.94</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4">
         <v>1.55</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>111.51</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.62</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>116.54</v>
       </c>
-      <c r="K4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="L4" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F5">
         <v>150.62</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5">
         <v>1.55</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>233.46</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.62</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>244</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" t="s">
-        <v>26</v>
       </c>
       <c r="F6">
         <v>61.86</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6">
         <v>1.55</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>95.88</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.6</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>98.98</v>
       </c>
-      <c r="K6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="L6" t="s">
+        <v>36</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F7">
         <v>142.02</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7">
         <v>1.47</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>208.77</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.51</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>214.45</v>
       </c>
-      <c r="K7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="L7" t="s">
+        <v>37</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F8">
         <v>70.77</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8">
         <v>1.47</v>
       </c>
-      <c r="H8">
+      <c r="I8" s="1">
         <v>104.03</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>1.51</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>106.86</v>
       </c>
-      <c r="K8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="L8" t="s">
         <v>38</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="5" t="s">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="6">
-        <v>613.04</v>
-      </c>
-      <c r="C13" s="6">
-        <v>7</v>
-      </c>
-      <c r="D13" s="7">
-        <v>1.529</v>
-      </c>
-      <c r="E13" s="6">
-        <v>937.36</v>
-      </c>
-      <c r="F13" s="6">
-        <v>973.89</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="8" t="s">
+      <c r="E9" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9">
+        <v>61.92</v>
+      </c>
+      <c r="G9" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9">
+        <v>1.45</v>
+      </c>
+      <c r="I9" s="1">
+        <v>89.78</v>
+      </c>
+      <c r="J9">
+        <v>1.51</v>
+      </c>
+      <c r="K9" s="1">
+        <v>93.5</v>
+      </c>
+      <c r="L9" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="9">
-        <v>613.04</v>
-      </c>
-      <c r="C14" s="9">
-        <v>7</v>
-      </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9">
-        <v>937.36</v>
-      </c>
-      <c r="F14" s="9">
-        <v>973.89</v>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="6">
+        <v>674.96</v>
+      </c>
+      <c r="C14" s="6">
+        <v>8</v>
+      </c>
+      <c r="D14" s="7">
+        <v>1.5218</v>
+      </c>
+      <c r="E14" s="6">
+        <v>1027.14</v>
+      </c>
+      <c r="F14" s="6">
+        <v>1067.39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="9">
+        <v>674.96</v>
+      </c>
+      <c r="C15" s="9">
+        <v>8</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="9">
+        <v>1027.14</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1067.39</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,6 +55,9 @@
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>2026-07-01</t>
   </si>
   <si>
@@ -67,13 +73,31 @@
     <t>2026-07-11</t>
   </si>
   <si>
-    <t>В.Търново</t>
-  </si>
-  <si>
-    <t>Варна Варненчик</t>
-  </si>
-  <si>
-    <t>Варна</t>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>2026-07-20</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>2026-07-28</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>1103 Велико Търново изход</t>
+  </si>
+  <si>
+    <t>1147 Варна Ситроен</t>
+  </si>
+  <si>
+    <t>1199 Varna Car Osvoboditel</t>
   </si>
   <si>
     <t>В1971ТТ</t>
@@ -103,22 +127,85 @@
     <t>DIESEL EKONOMY</t>
   </si>
   <si>
-    <t>2026-07-01 04:23:16</t>
-  </si>
-  <si>
-    <t>2026-07-04 00:57:55</t>
-  </si>
-  <si>
-    <t>2026-07-05 02:16:30</t>
-  </si>
-  <si>
-    <t>2026-07-09 20:11:17</t>
-  </si>
-  <si>
-    <t>2026-07-09 20:59:06</t>
-  </si>
-  <si>
-    <t>2026-07-11 11:09:57</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>04:24:00</t>
+  </si>
+  <si>
+    <t>00:57:00</t>
+  </si>
+  <si>
+    <t>02:16:00</t>
+  </si>
+  <si>
+    <t>20:11:00</t>
+  </si>
+  <si>
+    <t>20:59:00</t>
+  </si>
+  <si>
+    <t>11:10:00</t>
+  </si>
+  <si>
+    <t>21:03:00</t>
+  </si>
+  <si>
+    <t>10:33:00</t>
+  </si>
+  <si>
+    <t>21:37:00</t>
+  </si>
+  <si>
+    <t>15:57:00</t>
+  </si>
+  <si>
+    <t>21:12:00</t>
+  </si>
+  <si>
+    <t>12:39:00</t>
+  </si>
+  <si>
+    <t>20:46:00</t>
+  </si>
+  <si>
+    <t>3234153606 3234153606</t>
+  </si>
+  <si>
+    <t>3234299071 3234299071</t>
+  </si>
+  <si>
+    <t>3234328941 3234328941</t>
+  </si>
+  <si>
+    <t>3234550298 3234550298</t>
+  </si>
+  <si>
+    <t>3234556518 3234556518</t>
+  </si>
+  <si>
+    <t>3234630061 3234630061</t>
+  </si>
+  <si>
+    <t>3234961964 3234961964</t>
+  </si>
+  <si>
+    <t>3235088096 3235088096</t>
+  </si>
+  <si>
+    <t>3235152645 3235152645</t>
+  </si>
+  <si>
+    <t>3235434984 3235434984</t>
+  </si>
+  <si>
+    <t>3235439879 3235439879</t>
+  </si>
+  <si>
+    <t>3235480557 3235480557</t>
+  </si>
+  <si>
+    <t>3235595353 3235595353</t>
   </si>
   <si>
     <t>Общи литри по продукт / ДОК ТРАНС ЕООД</t>
@@ -536,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -545,15 +632,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -590,306 +679,656 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
         <v>1.44</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>144</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>1.51</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>151</v>
       </c>
-      <c r="K2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2">
+      <c r="L2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12">
+      <c r="N2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>127</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3">
         <v>1.45</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="1">
         <v>184.15</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>1.52</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>193.04</v>
       </c>
-      <c r="K3" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>65.51000000000001</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4">
         <v>1.45</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="1">
         <v>94.98999999999999</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>1.52</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>99.58</v>
       </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4">
+      <c r="L4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="N4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>95</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5">
         <v>1.45</v>
       </c>
-      <c r="H5">
+      <c r="I5" s="1">
         <v>137.75</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5">
         <v>1.52</v>
       </c>
-      <c r="J5">
+      <c r="K5" s="1">
         <v>144.4</v>
       </c>
-      <c r="K5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5">
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12">
+      <c r="N5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>150.01</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6">
         <v>1.45</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="1">
         <v>217.51</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6">
         <v>1.52</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="1">
         <v>228.02</v>
       </c>
-      <c r="K6" t="s">
-        <v>33</v>
-      </c>
-      <c r="L6">
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12">
+      <c r="N6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F7">
         <v>58.82</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7">
         <v>1.48</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="1">
         <v>87.05</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>1.54</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>90.58</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8">
+        <v>53.54</v>
+      </c>
+      <c r="G8" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8">
+        <v>1.54</v>
+      </c>
+      <c r="I8" s="1">
+        <v>82.45</v>
+      </c>
+      <c r="J8">
+        <v>1.63</v>
+      </c>
+      <c r="K8" s="1">
+        <v>87.27</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="L7">
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>142</v>
+      </c>
+      <c r="G9" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9">
+        <v>1.58</v>
+      </c>
+      <c r="I9" s="1">
+        <v>224.36</v>
+      </c>
+      <c r="J9">
+        <v>1.68</v>
+      </c>
+      <c r="K9" s="1">
+        <v>238.56</v>
+      </c>
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="3" t="s">
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10">
+        <v>102</v>
+      </c>
+      <c r="G10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10">
+        <v>1.59</v>
+      </c>
+      <c r="I10" s="1">
+        <v>162.18</v>
+      </c>
+      <c r="J10">
+        <v>1.68</v>
+      </c>
+      <c r="K10" s="1">
+        <v>171.36</v>
+      </c>
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11">
+        <v>103</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11">
+        <v>1.65</v>
+      </c>
+      <c r="I11" s="1">
+        <v>169.95</v>
+      </c>
+      <c r="J11">
+        <v>1.75</v>
+      </c>
+      <c r="K11" s="1">
+        <v>180.25</v>
+      </c>
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="F12">
+        <v>58.85</v>
+      </c>
+      <c r="G12" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="6">
-        <v>596.34</v>
-      </c>
-      <c r="C12" s="6">
-        <v>6</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.4513</v>
-      </c>
-      <c r="E12" s="6">
-        <v>865.45</v>
-      </c>
-      <c r="F12" s="6">
-        <v>906.62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B13" s="9">
-        <v>596.34</v>
-      </c>
-      <c r="C13" s="9">
-        <v>6</v>
-      </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9">
-        <v>865.45</v>
-      </c>
-      <c r="F13" s="9">
-        <v>906.62</v>
+      <c r="H12">
+        <v>1.65</v>
+      </c>
+      <c r="I12" s="1">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="J12">
+        <v>1.75</v>
+      </c>
+      <c r="K12" s="1">
+        <v>102.99</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13">
+        <v>38.01</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13">
+        <v>1.68</v>
+      </c>
+      <c r="I13" s="1">
+        <v>63.86</v>
+      </c>
+      <c r="J13">
+        <v>1.75</v>
+      </c>
+      <c r="K13" s="1">
+        <v>66.52</v>
+      </c>
+      <c r="L13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14">
+        <v>43</v>
+      </c>
+      <c r="G14" t="s">
+        <v>37</v>
+      </c>
+      <c r="H14">
+        <v>1.7</v>
+      </c>
+      <c r="I14" s="1">
+        <v>73.09999999999999</v>
+      </c>
+      <c r="J14">
+        <v>1.76</v>
+      </c>
+      <c r="K14" s="1">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="L14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" s="6">
+        <v>1136.74</v>
+      </c>
+      <c r="C19" s="6">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7">
+        <v>1.5293</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1738.45</v>
+      </c>
+      <c r="F19" s="6">
+        <v>1829.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="9">
+        <v>1136.74</v>
+      </c>
+      <c r="C20" s="9">
+        <v>13</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="9">
+        <v>1738.45</v>
+      </c>
+      <c r="F20" s="9">
+        <v>1829.25</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A17:F17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -232,7 +232,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1299,7 +1299,7 @@
         <v>13</v>
       </c>
       <c r="D19" s="7">
-        <v>1.5293</v>
+        <v>1.529329</v>
       </c>
       <c r="E19" s="6">
         <v>1738.45</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="71">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -623,7 +626,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -636,13 +639,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -685,582 +688,624 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.439</v>
+      </c>
+      <c r="J2">
+        <v>143.9</v>
+      </c>
+      <c r="K2" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="L2" s="1">
+        <v>151</v>
+      </c>
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E3" t="s">
         <v>37</v>
-      </c>
-      <c r="H2">
-        <v>1.44</v>
-      </c>
-      <c r="I2" s="1">
-        <v>144</v>
-      </c>
-      <c r="J2">
-        <v>1.51</v>
-      </c>
-      <c r="K2" s="1">
-        <v>151</v>
-      </c>
-      <c r="L2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>36</v>
       </c>
       <c r="F3">
         <v>127</v>
       </c>
       <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>1.406</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J3">
+        <v>183.642</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L3" s="1">
+        <v>193.04</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" t="s">
         <v>37</v>
       </c>
-      <c r="H3">
-        <v>1.45</v>
-      </c>
-      <c r="I3" s="1">
-        <v>184.15</v>
-      </c>
-      <c r="J3">
+      <c r="F4">
+        <v>65.51300000000001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4">
+        <v>1.406</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.446</v>
+      </c>
+      <c r="J4">
+        <v>94.731798</v>
+      </c>
+      <c r="K4" s="1">
         <v>1.52</v>
       </c>
-      <c r="K3" s="1">
-        <v>193.04</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3">
+      <c r="L4" s="1">
+        <v>99.57975999999999</v>
+      </c>
+      <c r="M4" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="O4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>33</v>
       </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4">
-        <v>65.51000000000001</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="E5" t="s">
         <v>37</v>
-      </c>
-      <c r="H4">
-        <v>1.45</v>
-      </c>
-      <c r="I4" s="1">
-        <v>94.98999999999999</v>
-      </c>
-      <c r="J4">
-        <v>1.52</v>
-      </c>
-      <c r="K4" s="1">
-        <v>99.58</v>
-      </c>
-      <c r="L4" t="s">
-        <v>40</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
       </c>
       <c r="F5">
         <v>95</v>
       </c>
       <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5">
+        <v>1.412</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J5">
+        <v>137.94</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="L5" s="1">
+        <v>144.4</v>
+      </c>
+      <c r="M5" t="s">
+        <v>42</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="H5">
-        <v>1.45</v>
-      </c>
-      <c r="I5" s="1">
-        <v>137.75</v>
-      </c>
-      <c r="J5">
+      <c r="F6">
+        <v>150.013</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6">
+        <v>1.412</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.452</v>
+      </c>
+      <c r="J6">
+        <v>217.818876</v>
+      </c>
+      <c r="K6" s="1">
         <v>1.52</v>
       </c>
-      <c r="K5" s="1">
-        <v>144.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5">
+      <c r="L6" s="1">
+        <v>228.01976</v>
+      </c>
+      <c r="M6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="O6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
         <v>27</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7">
+        <v>58.818</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7">
+        <v>1.437</v>
+      </c>
+      <c r="I7" s="1">
+        <v>1.477</v>
+      </c>
+      <c r="J7">
+        <v>86.87418599999999</v>
+      </c>
+      <c r="K7" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L7" s="1">
+        <v>90.57971999999999</v>
+      </c>
+      <c r="M7" t="s">
+        <v>44</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>30</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6">
-        <v>150.01</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="E8" t="s">
         <v>37</v>
-      </c>
-      <c r="H6">
-        <v>1.45</v>
-      </c>
-      <c r="I6" s="1">
-        <v>217.51</v>
-      </c>
-      <c r="J6">
-        <v>1.52</v>
-      </c>
-      <c r="K6" s="1">
-        <v>228.02</v>
-      </c>
-      <c r="L6" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7">
-        <v>58.82</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7">
-        <v>1.48</v>
-      </c>
-      <c r="I7" s="1">
-        <v>87.05</v>
-      </c>
-      <c r="J7">
-        <v>1.54</v>
-      </c>
-      <c r="K7" s="1">
-        <v>90.58</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>36</v>
       </c>
       <c r="F8">
         <v>53.54</v>
       </c>
       <c r="G8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8">
+        <v>1.499</v>
+      </c>
+      <c r="I8" s="1">
+        <v>1.539</v>
+      </c>
+      <c r="J8">
+        <v>82.39806</v>
+      </c>
+      <c r="K8" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="L8" s="1">
+        <v>87.2702</v>
+      </c>
+      <c r="M8" t="s">
+        <v>45</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" t="s">
         <v>37</v>
-      </c>
-      <c r="H8">
-        <v>1.54</v>
-      </c>
-      <c r="I8" s="1">
-        <v>82.45</v>
-      </c>
-      <c r="J8">
-        <v>1.63</v>
-      </c>
-      <c r="K8" s="1">
-        <v>87.27</v>
-      </c>
-      <c r="L8" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" t="s">
-        <v>36</v>
       </c>
       <c r="F9">
         <v>142</v>
       </c>
       <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9">
+        <v>1.546</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1.576</v>
+      </c>
+      <c r="J9">
+        <v>223.792</v>
+      </c>
+      <c r="K9" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L9" s="1">
+        <v>238.56</v>
+      </c>
+      <c r="M9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" t="s">
         <v>37</v>
-      </c>
-      <c r="H9">
-        <v>1.58</v>
-      </c>
-      <c r="I9" s="1">
-        <v>224.36</v>
-      </c>
-      <c r="J9">
-        <v>1.68</v>
-      </c>
-      <c r="K9" s="1">
-        <v>238.56</v>
-      </c>
-      <c r="L9" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" t="s">
-        <v>36</v>
       </c>
       <c r="F10">
         <v>102</v>
       </c>
       <c r="G10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10">
+        <v>1.564</v>
+      </c>
+      <c r="I10" s="1">
+        <v>1.594</v>
+      </c>
+      <c r="J10">
+        <v>162.588</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1.68</v>
+      </c>
+      <c r="L10" s="1">
+        <v>171.36</v>
+      </c>
+      <c r="M10" t="s">
+        <v>47</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" t="s">
         <v>37</v>
-      </c>
-      <c r="H10">
-        <v>1.59</v>
-      </c>
-      <c r="I10" s="1">
-        <v>162.18</v>
-      </c>
-      <c r="J10">
-        <v>1.68</v>
-      </c>
-      <c r="K10" s="1">
-        <v>171.36</v>
-      </c>
-      <c r="L10" t="s">
-        <v>46</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" t="s">
-        <v>36</v>
       </c>
       <c r="F11">
         <v>103</v>
       </c>
       <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11">
+        <v>1.619</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J11">
+        <v>169.847</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.75</v>
+      </c>
+      <c r="L11" s="1">
+        <v>180.25</v>
+      </c>
+      <c r="M11" t="s">
+        <v>48</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
         <v>37</v>
       </c>
-      <c r="H11">
-        <v>1.65</v>
-      </c>
-      <c r="I11" s="1">
-        <v>169.95</v>
-      </c>
-      <c r="J11">
+      <c r="F12">
+        <v>58.851</v>
+      </c>
+      <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>1.619</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.649</v>
+      </c>
+      <c r="J12">
+        <v>97.045299</v>
+      </c>
+      <c r="K12" s="1">
         <v>1.75</v>
       </c>
-      <c r="K11" s="1">
-        <v>180.25</v>
-      </c>
-      <c r="L11" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11">
+      <c r="L12" s="1">
+        <v>102.98925</v>
+      </c>
+      <c r="M12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N12">
         <v>0</v>
       </c>
-      <c r="N11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12">
-        <v>58.85</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="O12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" t="s">
         <v>37</v>
       </c>
-      <c r="H12">
-        <v>1.65</v>
-      </c>
-      <c r="I12" s="1">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="J12">
+      <c r="F13">
+        <v>38.011</v>
+      </c>
+      <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13">
+        <v>1.653</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1.683</v>
+      </c>
+      <c r="J13">
+        <v>63.972513</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.75</v>
       </c>
-      <c r="K12" s="1">
-        <v>102.99</v>
-      </c>
-      <c r="L12" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12">
+      <c r="L13" s="1">
+        <v>66.51925</v>
+      </c>
+      <c r="M13" t="s">
+        <v>50</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13">
-        <v>38.01</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="O13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" t="s">
         <v>37</v>
-      </c>
-      <c r="H13">
-        <v>1.68</v>
-      </c>
-      <c r="I13" s="1">
-        <v>63.86</v>
-      </c>
-      <c r="J13">
-        <v>1.75</v>
-      </c>
-      <c r="K13" s="1">
-        <v>66.52</v>
-      </c>
-      <c r="L13" t="s">
-        <v>49</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" t="s">
-        <v>36</v>
       </c>
       <c r="F14">
         <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H14">
-        <v>1.7</v>
+        <v>1.674</v>
       </c>
       <c r="I14" s="1">
-        <v>73.09999999999999</v>
+        <v>1.704</v>
       </c>
       <c r="J14">
+        <v>73.27200000000001</v>
+      </c>
+      <c r="K14" s="1">
         <v>1.76</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>75.68000000000001</v>
       </c>
-      <c r="L14" t="s">
-        <v>50</v>
-      </c>
-      <c r="M14">
+      <c r="M14" t="s">
+        <v>51</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>63</v>
+      <c r="O14" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1270,39 +1315,39 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6">
-        <v>1136.74</v>
+        <v>1136.746</v>
       </c>
       <c r="C19" s="6">
         <v>13</v>
       </c>
       <c r="D19" s="7">
-        <v>1.529329</v>
+        <v>1.528769</v>
       </c>
       <c r="E19" s="6">
-        <v>1738.45</v>
+        <v>1737.82</v>
       </c>
       <c r="F19" s="6">
         <v>1829.25</v>
@@ -1310,17 +1355,17 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" s="9">
-        <v>1136.74</v>
+        <v>1136.746</v>
       </c>
       <c r="C20" s="9">
         <v>13</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9">
-        <v>1738.45</v>
+        <v>1737.82</v>
       </c>
       <c r="F20" s="9">
         <v>1829.25</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ДОК ТРАНС ЕООД/ДОК ТРАНС ЕООД.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="70">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -234,8 +231,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -328,10 +325,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,7 +623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -639,13 +636,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -688,624 +685,582 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F2">
         <v>100</v>
       </c>
       <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
+        <v>1.439</v>
+      </c>
+      <c r="I2" s="1">
+        <v>143.9</v>
+      </c>
+      <c r="J2">
+        <v>1.51</v>
+      </c>
+      <c r="K2" s="1">
+        <v>151</v>
+      </c>
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.439</v>
-      </c>
-      <c r="J2">
-        <v>143.9</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.51</v>
-      </c>
-      <c r="L2" s="1">
-        <v>151</v>
-      </c>
-      <c r="M2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="N2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3">
         <v>127</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I3" s="1">
-        <v>1.446</v>
+        <v>183.642</v>
       </c>
       <c r="J3">
-        <v>183.642</v>
+        <v>1.52</v>
       </c>
       <c r="K3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L3" s="1">
         <v>193.04</v>
       </c>
-      <c r="M3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+      <c r="N3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F4">
         <v>65.51300000000001</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H4">
-        <v>1.406</v>
+        <v>1.446</v>
       </c>
       <c r="I4" s="1">
-        <v>1.446</v>
+        <v>94.732</v>
       </c>
       <c r="J4">
-        <v>94.731798</v>
+        <v>1.52</v>
       </c>
       <c r="K4" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L4" s="1">
-        <v>99.57975999999999</v>
-      </c>
-      <c r="M4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4">
+        <v>99.58</v>
+      </c>
+      <c r="L4" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4">
         <v>0</v>
       </c>
-      <c r="O4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="N4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F5">
         <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H5">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I5" s="1">
-        <v>1.452</v>
+        <v>137.94</v>
       </c>
       <c r="J5">
-        <v>137.94</v>
+        <v>1.52</v>
       </c>
       <c r="K5" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L5" s="1">
         <v>144.4</v>
       </c>
-      <c r="M5" t="s">
-        <v>42</v>
-      </c>
-      <c r="N5">
+      <c r="L5" t="s">
+        <v>41</v>
+      </c>
+      <c r="M5">
         <v>0</v>
       </c>
-      <c r="O5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+      <c r="N5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>150.013</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H6">
-        <v>1.412</v>
+        <v>1.452</v>
       </c>
       <c r="I6" s="1">
-        <v>1.452</v>
+        <v>217.819</v>
       </c>
       <c r="J6">
-        <v>217.818876</v>
+        <v>1.52</v>
       </c>
       <c r="K6" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="L6" s="1">
-        <v>228.01976</v>
-      </c>
-      <c r="M6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6">
+        <v>228.02</v>
+      </c>
+      <c r="L6" t="s">
+        <v>42</v>
+      </c>
+      <c r="M6">
         <v>0</v>
       </c>
-      <c r="O6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+      <c r="N6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" t="s">
         <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>37</v>
       </c>
       <c r="F7">
         <v>58.818</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H7">
-        <v>1.437</v>
+        <v>1.477</v>
       </c>
       <c r="I7" s="1">
-        <v>1.477</v>
+        <v>86.874</v>
       </c>
       <c r="J7">
-        <v>86.87418599999999</v>
+        <v>1.54</v>
       </c>
       <c r="K7" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L7" s="1">
-        <v>90.57971999999999</v>
-      </c>
-      <c r="M7" t="s">
-        <v>44</v>
-      </c>
-      <c r="N7">
+        <v>90.58</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7">
         <v>0</v>
       </c>
-      <c r="O7" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="N7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F8">
         <v>53.54</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8">
-        <v>1.499</v>
+        <v>1.539</v>
       </c>
       <c r="I8" s="1">
-        <v>1.539</v>
+        <v>82.398</v>
       </c>
       <c r="J8">
-        <v>82.39806</v>
+        <v>1.63</v>
       </c>
       <c r="K8" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L8" s="1">
-        <v>87.2702</v>
-      </c>
-      <c r="M8" t="s">
-        <v>45</v>
-      </c>
-      <c r="N8">
+        <v>87.27</v>
+      </c>
+      <c r="L8" t="s">
+        <v>44</v>
+      </c>
+      <c r="M8">
         <v>0</v>
       </c>
-      <c r="O8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="N8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F9">
         <v>142</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H9">
-        <v>1.546</v>
+        <v>1.576</v>
       </c>
       <c r="I9" s="1">
-        <v>1.576</v>
+        <v>223.792</v>
       </c>
       <c r="J9">
-        <v>223.792</v>
+        <v>1.68</v>
       </c>
       <c r="K9" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L9" s="1">
         <v>238.56</v>
       </c>
-      <c r="M9" t="s">
-        <v>46</v>
-      </c>
-      <c r="N9">
+      <c r="L9" t="s">
+        <v>45</v>
+      </c>
+      <c r="M9">
         <v>0</v>
       </c>
-      <c r="O9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="N9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F10">
         <v>102</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H10">
-        <v>1.564</v>
+        <v>1.594</v>
       </c>
       <c r="I10" s="1">
-        <v>1.594</v>
+        <v>162.588</v>
       </c>
       <c r="J10">
-        <v>162.588</v>
+        <v>1.68</v>
       </c>
       <c r="K10" s="1">
-        <v>1.68</v>
-      </c>
-      <c r="L10" s="1">
         <v>171.36</v>
       </c>
-      <c r="M10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N10">
+      <c r="L10" t="s">
+        <v>46</v>
+      </c>
+      <c r="M10">
         <v>0</v>
       </c>
-      <c r="O10" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="N10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11">
         <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H11">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I11" s="1">
-        <v>1.649</v>
+        <v>169.847</v>
       </c>
       <c r="J11">
-        <v>169.847</v>
+        <v>1.75</v>
       </c>
       <c r="K11" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L11" s="1">
         <v>180.25</v>
       </c>
-      <c r="M11" t="s">
-        <v>48</v>
-      </c>
-      <c r="N11">
+      <c r="L11" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11">
         <v>0</v>
       </c>
-      <c r="O11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="N11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
       </c>
       <c r="F12">
         <v>58.851</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H12">
-        <v>1.619</v>
+        <v>1.649</v>
       </c>
       <c r="I12" s="1">
-        <v>1.649</v>
+        <v>97.045</v>
       </c>
       <c r="J12">
-        <v>97.045299</v>
+        <v>1.75</v>
       </c>
       <c r="K12" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L12" s="1">
-        <v>102.98925</v>
-      </c>
-      <c r="M12" t="s">
-        <v>49</v>
-      </c>
-      <c r="N12">
+        <v>102.989</v>
+      </c>
+      <c r="L12" t="s">
+        <v>48</v>
+      </c>
+      <c r="M12">
         <v>0</v>
       </c>
-      <c r="O12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+      <c r="N12" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13">
         <v>38.011</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H13">
-        <v>1.653</v>
+        <v>1.683</v>
       </c>
       <c r="I13" s="1">
-        <v>1.683</v>
+        <v>63.973</v>
       </c>
       <c r="J13">
-        <v>63.972513</v>
+        <v>1.75</v>
       </c>
       <c r="K13" s="1">
-        <v>1.75</v>
-      </c>
-      <c r="L13" s="1">
-        <v>66.51925</v>
-      </c>
-      <c r="M13" t="s">
-        <v>50</v>
-      </c>
-      <c r="N13">
+        <v>66.51900000000001</v>
+      </c>
+      <c r="L13" t="s">
+        <v>49</v>
+      </c>
+      <c r="M13">
         <v>0</v>
       </c>
-      <c r="O13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+      <c r="N13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14">
         <v>43</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H14">
-        <v>1.674</v>
+        <v>1.704</v>
       </c>
       <c r="I14" s="1">
-        <v>1.704</v>
+        <v>73.27200000000001</v>
       </c>
       <c r="J14">
-        <v>73.27200000000001</v>
+        <v>1.76</v>
       </c>
       <c r="K14" s="1">
-        <v>1.76</v>
-      </c>
-      <c r="L14" s="1">
         <v>75.68000000000001</v>
       </c>
-      <c r="M14" t="s">
-        <v>51</v>
-      </c>
-      <c r="N14">
+      <c r="L14" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14">
         <v>0</v>
       </c>
-      <c r="O14" t="s">
-        <v>64</v>
+      <c r="N14" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1315,47 +1270,47 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="C18" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="D18" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="E18" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="6">
         <v>1136.746</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="7">
         <v>13</v>
       </c>
       <c r="D19" s="7">
-        <v>1.528769</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1737.82</v>
-      </c>
-      <c r="F19" s="6">
-        <v>1829.25</v>
+        <v>1.529</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1737.822</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1829.248</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B20" s="9">
         <v>1136.746</v>
@@ -1365,10 +1320,10 @@
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9">
-        <v>1737.82</v>
+        <v>1737.822</v>
       </c>
       <c r="F20" s="9">
-        <v>1829.25</v>
+        <v>1829.248</v>
       </c>
     </row>
   </sheetData>
